--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R7a6f97e424104562"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R75c9e1d8fa2f43e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R04e8a8c26930463e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R3a56515cfcbb4076"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R79ce645c53c14e24"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Ra79e9f7dd1bf4351"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R04e8a8c26930463e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R3a56515cfcbb4076"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R3f82e3b033044a6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rfa8bbfdc58bf4b31"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Ra79e9f7dd1bf4351"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R5d656ec5b4e34be9"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R3f82e3b033044a6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rfa8bbfdc58bf4b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rff7550a063ef4b81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R0cfedd67cfd2411b"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R5d656ec5b4e34be9"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rf0358b1c91574663"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rff7550a063ef4b81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R0cfedd67cfd2411b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rb2bc5708c1e64d71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Ra61b0bf2254f4fe9"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rf0358b1c91574663"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rd5943e05fa26428b"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rb2bc5708c1e64d71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Ra61b0bf2254f4fe9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R9f7af812ecc14ac5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R21ed2186e0d04828"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rd5943e05fa26428b"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rad8fcaa0f61f464b"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R9f7af812ecc14ac5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R21ed2186e0d04828"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R04b6b202bf9b4f11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Recc2db21c1be40a1"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rad8fcaa0f61f464b"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R2726c5283ed24665"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R04b6b202bf9b4f11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Recc2db21c1be40a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rf4dca42fee25415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R9c18f05783a647e3"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R2726c5283ed24665"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rc0f34c4cb94c4953"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rf4dca42fee25415d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R9c18f05783a647e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R88676228fb4a4255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R52aeea9202a24feb"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rc0f34c4cb94c4953"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R01e2914908114e69"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R88676228fb4a4255"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R52aeea9202a24feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R31122c2be3f645ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rffd5360f40094011"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R01e2914908114e69"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rf5f24bb1fd2749c5"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R31122c2be3f645ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rffd5360f40094011"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R48ccc9d1a2ca4d31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R2430af4bb8794ab8"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rf5f24bb1fd2749c5"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rac126fd20737419f"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R48ccc9d1a2ca4d31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R2430af4bb8794ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rf09e842629594acf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R275e12e7d30c4bcc"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rac126fd20737419f"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0daf4b32363d4219"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rf09e842629594acf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R275e12e7d30c4bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R8d2f6e5d872847b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R8c4da591af4d4be8"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0daf4b32363d4219"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Re5e7c3928ef04315"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R8d2f6e5d872847b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R8c4da591af4d4be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R36f7cf107d3a4dc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R9d4c8143f23b4130"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Re5e7c3928ef04315"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R6fc50b7188b448d2"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R36f7cf107d3a4dc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R9d4c8143f23b4130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rd56fe8b10c354d80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rfaabc72ff65343b1"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R6fc50b7188b448d2"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R75e6e7ea5e6e4a27"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
